--- a/data/danhmucxa.xlsx
+++ b/data/danhmucxa.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QLBHXHTN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\THEO DOI BHXH TN\QLBHXHTN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8448E432-65A9-44B0-8379-E62B2DB2AEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2E6B67B1-B221-4BF3-822F-21969796398B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="25824" windowHeight="15504"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -724,15 +723,6 @@
     <t>TÂN HƯNG</t>
   </si>
   <si>
-    <t>Ma_Don_Vi</t>
-  </si>
-  <si>
-    <t>Ten_Xa</t>
-  </si>
-  <si>
-    <t>Chi_Tieu</t>
-  </si>
-  <si>
     <t>IS0109E</t>
   </si>
   <si>
@@ -866,15 +856,24 @@
   </si>
   <si>
     <t>ISDVC06</t>
+  </si>
+  <si>
+    <t>Mã đơn vị</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu</t>
+  </si>
+  <si>
+    <t>Tên Xã / Đơn Vị</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -892,15 +891,14 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -917,7 +915,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -984,10 +982,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1000,15 +1013,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1300,26 +1315,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860A532E-4BA9-4595-8796-19AC0FABDC8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H285"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>231</v>
+    <row r="1" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="C1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>29</v>
       </c>
@@ -1338,7 +1353,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -1365,7 +1380,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1376,7 +1391,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1395,7 +1410,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1411,7 +1426,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>39</v>
       </c>
@@ -1422,7 +1437,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>40</v>
       </c>
@@ -1438,7 +1453,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
@@ -1457,7 +1472,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
@@ -1473,7 +1488,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>46</v>
       </c>
@@ -1489,7 +1504,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
@@ -1513,7 +1528,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
@@ -1529,7 +1544,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>53</v>
       </c>
@@ -1537,7 +1552,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>54</v>
       </c>
@@ -1577,7 +1592,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>59</v>
       </c>
@@ -1609,7 +1624,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>63</v>
       </c>
@@ -1625,7 +1640,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>65</v>
       </c>
@@ -1641,7 +1656,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>67</v>
       </c>
@@ -1649,7 +1664,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>68</v>
       </c>
@@ -1657,7 +1672,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>69</v>
       </c>
@@ -1673,7 +1688,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>71</v>
       </c>
@@ -1689,7 +1704,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>73</v>
       </c>
@@ -1705,7 +1720,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>75</v>
       </c>
@@ -1713,7 +1728,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>76</v>
       </c>
@@ -1721,7 +1736,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>77</v>
       </c>
@@ -1729,7 +1744,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>78</v>
       </c>
@@ -1745,7 +1760,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>80</v>
       </c>
@@ -1761,7 +1776,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>82</v>
       </c>
@@ -1777,7 +1792,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>84</v>
       </c>
@@ -1788,7 +1803,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>85</v>
       </c>
@@ -1796,7 +1811,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>86</v>
       </c>
@@ -1804,7 +1819,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>87</v>
       </c>
@@ -1844,7 +1859,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -1852,7 +1867,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>93</v>
       </c>
@@ -1868,7 +1883,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>95</v>
       </c>
@@ -1884,7 +1899,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>97</v>
       </c>
@@ -1892,7 +1907,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>98</v>
       </c>
@@ -1908,7 +1923,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>100</v>
       </c>
@@ -1940,7 +1955,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>104</v>
       </c>
@@ -2004,7 +2019,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>112</v>
       </c>
@@ -2052,7 +2067,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>118</v>
       </c>
@@ -2068,7 +2083,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>120</v>
       </c>
@@ -2308,7 +2323,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>150</v>
       </c>
@@ -2324,7 +2339,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>152</v>
       </c>
@@ -2340,7 +2355,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>154</v>
       </c>
@@ -2348,7 +2363,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>155</v>
       </c>
@@ -2356,7 +2371,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>156</v>
       </c>
@@ -2364,7 +2379,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>157</v>
       </c>
@@ -2372,7 +2387,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>158</v>
       </c>
@@ -2380,7 +2395,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>159</v>
       </c>
@@ -2388,7 +2403,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>160</v>
       </c>
@@ -2396,7 +2411,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>161</v>
       </c>
@@ -2404,7 +2419,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>162</v>
       </c>
@@ -2412,7 +2427,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>163</v>
       </c>
@@ -2420,7 +2435,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>164</v>
       </c>
@@ -2428,7 +2443,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>165</v>
       </c>
@@ -2436,7 +2451,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>166</v>
       </c>
@@ -2444,7 +2459,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>167</v>
       </c>
@@ -2452,7 +2467,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>168</v>
       </c>
@@ -2460,7 +2475,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>169</v>
       </c>
@@ -2468,7 +2483,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>170</v>
       </c>
@@ -2476,7 +2491,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>171</v>
       </c>
@@ -2484,7 +2499,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>172</v>
       </c>
@@ -2492,7 +2507,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>173</v>
       </c>
@@ -2500,7 +2515,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>174</v>
       </c>
@@ -2508,7 +2523,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>175</v>
       </c>
@@ -2516,7 +2531,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>176</v>
       </c>
@@ -2524,7 +2539,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>177</v>
       </c>
@@ -2532,7 +2547,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>178</v>
       </c>
@@ -2540,7 +2555,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>179</v>
       </c>
@@ -2548,7 +2563,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>180</v>
       </c>
@@ -2556,7 +2571,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>181</v>
       </c>
@@ -2564,7 +2579,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>182</v>
       </c>
@@ -2572,7 +2587,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>183</v>
       </c>
@@ -2580,7 +2595,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>184</v>
       </c>
@@ -2588,7 +2603,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>185</v>
       </c>
@@ -2596,7 +2611,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>186</v>
       </c>
@@ -2604,7 +2619,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>187</v>
       </c>
@@ -2612,7 +2627,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>188</v>
       </c>
@@ -2620,7 +2635,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>189</v>
       </c>
@@ -2628,7 +2643,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>190</v>
       </c>
@@ -2636,7 +2651,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>191</v>
       </c>
@@ -2644,7 +2659,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>192</v>
       </c>
@@ -2652,7 +2667,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>193</v>
       </c>
@@ -2780,7 +2795,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>209</v>
       </c>
@@ -2804,7 +2819,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>212</v>
       </c>
@@ -2820,7 +2835,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>214</v>
       </c>
@@ -2884,7 +2899,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>0</v>
       </c>
@@ -2892,7 +2907,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="40.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>1</v>
       </c>
@@ -2908,7 +2923,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>3</v>
       </c>
@@ -2916,7 +2931,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>4</v>
       </c>
@@ -2932,7 +2947,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>6</v>
       </c>
@@ -2940,7 +2955,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>7</v>
       </c>
@@ -2948,7 +2963,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>8</v>
       </c>
@@ -2964,7 +2979,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>10</v>
       </c>
@@ -2972,7 +2987,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>11</v>
       </c>
@@ -2980,7 +2995,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>12</v>
       </c>
@@ -2988,7 +3003,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>13</v>
       </c>
@@ -2996,7 +3011,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>14</v>
       </c>
@@ -3004,7 +3019,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>15</v>
       </c>
@@ -3020,7 +3035,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>17</v>
       </c>
@@ -3028,7 +3043,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>18</v>
       </c>
@@ -3036,7 +3051,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -3044,7 +3059,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>20</v>
       </c>
@@ -3052,7 +3067,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>21</v>
       </c>
@@ -3068,7 +3083,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>23</v>
       </c>
@@ -3076,7 +3091,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>24</v>
       </c>
@@ -3084,7 +3099,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>25</v>
       </c>
@@ -3092,7 +3107,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,7 +3115,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>27</v>
       </c>
@@ -3109,7 +3124,7 @@
       </c>
       <c r="H222" s="4"/>
     </row>
-    <row r="223" spans="1:8" ht="30.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>28</v>
       </c>
@@ -3117,419 +3132,419 @@
         <v>228</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="26" x14ac:dyDescent="0.25">
-      <c r="A224" s="6" t="s">
+    <row r="224" spans="1:8" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A224" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A227" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B224" s="6" t="s">
+      <c r="B227" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A225" s="6" t="s">
+    <row r="228" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A228" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B225" s="6" t="s">
+      <c r="B228" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A229" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A230" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A231" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A232" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A233" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B233" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A226" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" ht="26" x14ac:dyDescent="0.25">
-      <c r="A227" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" ht="26" x14ac:dyDescent="0.25">
-      <c r="A228" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A229" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B229" s="6" t="s">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A234" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A235" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A236" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A237" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A238" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B238" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A230" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="231" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A231" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A232" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="233" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A233" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B233" s="7" t="s">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A239" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A240" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A241" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A242" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A243" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B243" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A234" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B234" s="7" t="s">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A244" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B244" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A235" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="B235" s="7" t="s">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B245" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A236" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="B236" s="7" t="s">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A246" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B246" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A237" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="B237" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A238" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="B238" s="7" t="s">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A247" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B247" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A239" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="B239" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A240" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="B240" s="7" t="s">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A248" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B248" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A241" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="B241" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A242" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A243" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B243" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A244" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="B244" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A245" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B245" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A246" s="8" t="s">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A249" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B246" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A247" s="8" t="s">
+      <c r="B249" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A250" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B247" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A248" s="8" t="s">
+      <c r="B250" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A251" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B248" s="7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A249" s="8" t="s">
+      <c r="B251" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A252" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B249" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A250" s="8" t="s">
+      <c r="B252" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A253" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B250" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A251" s="8" t="s">
+      <c r="B253" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A254" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="B251" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A252" s="8" t="s">
+      <c r="B254" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A255" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B252" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A253" s="8" t="s">
+      <c r="B255" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A256" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B253" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A254" s="8" t="s">
+      <c r="B256" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A257" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="B254" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A255" s="8" t="s">
+      <c r="B257" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A258" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B255" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="256" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A256" s="8" t="s">
+      <c r="B258" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A259" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B256" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A257" s="8" t="s">
+      <c r="B259" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A260" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B257" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A258" s="8" t="s">
+      <c r="B260" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B258" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A259" s="8" t="s">
+      <c r="B261" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A262" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B259" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A260" s="8" t="s">
+      <c r="B262" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A263" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B260" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A261" s="8" t="s">
+      <c r="B263" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="B261" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A262" s="8" t="s">
+      <c r="B264" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="B262" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A263" s="8" t="s">
+      <c r="B265" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B263" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A264" s="8" t="s">
+      <c r="B266" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B264" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A265" s="8" t="s">
+      <c r="B267" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="B265" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A266" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="B266" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A267" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B267" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A268" s="8" t="s">
-        <v>277</v>
-      </c>
-      <c r="B268" s="7" t="s">
+      <c r="B268" s="6" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="8"/>
+      <c r="A269" s="7"/>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="8"/>
+      <c r="A270" s="7"/>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="8"/>
+      <c r="A271" s="7"/>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="8"/>
+      <c r="A272" s="7"/>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A273" s="8"/>
+      <c r="A273" s="7"/>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A274" s="8"/>
+      <c r="A274" s="7"/>
     </row>
     <row r="275" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A275" s="8"/>
+      <c r="A275" s="7"/>
     </row>
     <row r="276" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A276" s="8"/>
+      <c r="A276" s="7"/>
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A277" s="8"/>
+      <c r="A277" s="7"/>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A278" s="8"/>
+      <c r="A278" s="7"/>
     </row>
     <row r="279" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A279" s="8"/>
+      <c r="A279" s="7"/>
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A280" s="8"/>
+      <c r="A280" s="7"/>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A281" s="8"/>
+      <c r="A281" s="7"/>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A282" s="8"/>
+      <c r="A282" s="7"/>
     </row>
     <row r="283" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A283" s="8"/>
+      <c r="A283" s="7"/>
     </row>
     <row r="284" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A284" s="8"/>
+      <c r="A284" s="7"/>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A285" s="8"/>
+      <c r="A285" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1048576">
+  <conditionalFormatting sqref="A2:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
